--- a/public/templates/setters-markers-template.xlsx
+++ b/public/templates/setters-markers-template.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="Teachers">Deployment!$A$4:$A$10,Deployment!$B$4:$B$10,Deployment!$C$4:$C$10,Deployment!$D$4:$D$10</definedName>
+    <definedName name="Teachers">Deployment!$W$4:$W$29</definedName>
     <definedName name="Assessments">Lists!$A$2:$A$5</definedName>
     <definedName name="Streams">Lists!$B$2:$B$6</definedName>
     <definedName name="Terms">Lists!$C$2:$C$5</definedName>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V85"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -494,6 +494,7 @@
     <col width="5" customWidth="1" min="20" max="20"/>
     <col width="8" customWidth="1" min="21" max="21"/>
     <col width="30" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,6 +532,10 @@
           <t>Vikram</t>
         </is>
       </c>
+      <c r="W4">
+        <f>A4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -553,6 +558,10 @@
           <t>Wendy</t>
         </is>
       </c>
+      <c r="W5">
+        <f>A5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -575,6 +584,10 @@
           <t>Xavier</t>
         </is>
       </c>
+      <c r="W6">
+        <f>A6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -597,6 +610,10 @@
           <t>Yasmin</t>
         </is>
       </c>
+      <c r="W7">
+        <f>A7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -619,6 +636,10 @@
           <t>Zane</t>
         </is>
       </c>
+      <c r="W8">
+        <f>A8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -636,6 +657,10 @@
           <t>Tomas</t>
         </is>
       </c>
+      <c r="W9">
+        <f>A9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -653,6 +678,16 @@
           <t>Uma</t>
         </is>
       </c>
+      <c r="W10">
+        <f>A10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="W11">
+        <f>B4</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -765,12 +800,20 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="W12">
+        <f>B5</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>─── TERM 1 ───</t>
         </is>
+      </c>
+      <c r="W13">
+        <f>B6</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -845,6 +888,10 @@
           <t>Co-marked</t>
         </is>
       </c>
+      <c r="W14">
+        <f>B7</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -914,6 +961,10 @@
         <v/>
       </c>
       <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15">
+        <f>B8</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -981,6 +1032,10 @@
         <v/>
       </c>
       <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16">
+        <f>B9</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1050,6 +1105,10 @@
         <v/>
       </c>
       <c r="V17" s="3" t="inlineStr"/>
+      <c r="W17">
+        <f>B10</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1121,6 +1180,10 @@
           <t>Co-marked</t>
         </is>
       </c>
+      <c r="W18">
+        <f>C4</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1190,6 +1253,10 @@
         <v/>
       </c>
       <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19">
+        <f>C5</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1261,6 +1328,10 @@
           <t>G2 variant of G3 paper</t>
         </is>
       </c>
+      <c r="W20">
+        <f>C6</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1330,6 +1401,10 @@
         <v/>
       </c>
       <c r="V21" s="3" t="inlineStr"/>
+      <c r="W21">
+        <f>C7</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1402,6 +1477,10 @@
         <is>
           <t>Co-marked</t>
         </is>
+      </c>
+      <c r="W22">
+        <f>C8</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1474,6 +1553,10 @@
           <t>G2 variant of G3 paper</t>
         </is>
       </c>
+      <c r="W23">
+        <f>C9</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1541,6 +1624,10 @@
         <v/>
       </c>
       <c r="V24" s="3" t="inlineStr"/>
+      <c r="W24">
+        <f>C10</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1610,6 +1697,10 @@
         <v/>
       </c>
       <c r="V25" s="3" t="inlineStr"/>
+      <c r="W25">
+        <f>D4</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1682,6 +1773,10 @@
         <is>
           <t>Co-marked</t>
         </is>
+      </c>
+      <c r="W26">
+        <f>D5</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1750,6 +1845,10 @@
         <v/>
       </c>
       <c r="V27" s="3" t="inlineStr"/>
+      <c r="W27">
+        <f>D6</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1819,12 +1918,20 @@
         <v/>
       </c>
       <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28">
+        <f>D7</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>─── TERM 2 ───</t>
         </is>
+      </c>
+      <c r="W29">
+        <f>D8</f>
+        <v/>
       </c>
     </row>
     <row r="30">
